--- a/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}fhs-1:年齢[x]または生まれ[x]を持つことができますが、両方ではありません / Can have age[x] or born[x], but not both {age.empty() or born.empty()}fhs-2:年齢[x]が存在する場合にのみ推定される可能性があります / Can only have estimatedAge if age[x] is present {age.exists() or estimatedAge.empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}fhs-1:年齢[x]または生まれ[x]を持つことができますが、両方ではありません / Can have age[x] or born[x], but not both {age.empty() or born.empty()}fhs-2:年齢[x]が存在する場合にのみ推定される可能性があります / Can only have estimatedAge if age[x] is present {age.exists() or estimatedAge.empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -314,16 +314,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -449,7 +449,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -480,10 +480,10 @@
     <t>このレコードの外部ID / External Id(s) for this record</t>
   </si>
   <si>
-    <t>リソースが更新され、サーバーからサーバーに伝播するにつれて一定のままであるパフォーマーまたはその他のシステムによってこの家族の歴史に割り当てられたビジネス識別子。 / Business identifiers assigned to this family member history by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません（[ディスカッション]（Resource.html＃識別子を参照））。識別子が単一のリソースインスタンスにのみ表示することがベストプラクティスですが、ビジネス慣行は、同じ識別子を持つ複数のリソースインスタンスが存在する可能性があることを時々決定する場合があります。たとえば、複数の患者と個人のリソースインスタンスは、同じ社会保険番号を共有する場合があります。 / This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+    <t>リソースが更新され、サーバーからサーバーに伝播するにつれて一定のままであるパフォーマーまたはその他のシステムによってこの家族の歴史に割り当てられたビジネスidentifier。 / Business identifiers assigned to this family member history by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
+  </si>
+  <si>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません（[ディスカッション]（Resource.html＃identifierを参照））。identifierが単一のリソースインスタンスにのみ表示することがベストプラクティスですが、ビジネス慣行は、同じidentifierを持つ複数のリソースインスタンスが存在する可能性があることを時々決定する場合があります。たとえば、複数の患者と個人のリソースインスタンスは、同じ社会保険番号を共有する場合があります。 / This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
   </si>
   <si>
     <t>さまざまな参加システムで知られており、サーバー全体で一貫性を保っている方法で、家族の歴史を特定できます。 / Allows identification of the family member history as it is known by various participating systems and in a way that remains consistent across servers.</t>
@@ -526,7 +526,7 @@
     <t>URLは、外部からメンテナンスされたプロトコル、ガイドライン、オーダーセット、またはこのファミリーメンバー史によって全体または一部が順守されているその他の定義を指しています。 / The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this FamilyMemberHistory.</t>
   </si>
   <si>
-    <t>これは、HTMLページ、PDFなどである可能性があるか、単に解決できないURI識別子である可能性があります。 / This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+    <t>これは、HTMLページ、PDFなどである可能性があるか、単に解決できないURIidentifierである可能性があります。 / This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
   </si>
   <si>
     <t>Event.instantiatesUri</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
@@ -270,7 +270,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}fhs-1:年齢[x]または生まれ[x]を持つことができますが、両方ではありません / Can have age[x] or born[x], but not both {age.empty() or born.empty()}fhs-2:年齢[x]が存在する場合にのみ推定される可能性があります / Can only have estimatedAge if age[x] is present {age.exists() or estimatedAge.empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}fhs-1:年齢[x]または生まれ[x]を持つことができますが、両方ではありません / Can have age[x] or born[x], but not both {age.empty() or born.empty()}fhs-2:年齢[x]が存在する場合にのみ推定される可能性があります / Can only have estimatedAge if age[x] is present {age.exists() or estimatedAge.empty()}</t>
   </si>
   <si>
     <t>Event</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
@@ -535,7 +535,7 @@
     <t>FamilyMemberHistory.status</t>
   </si>
   <si>
-    <t>部分的|完了|エラーに入った|健康と知られていない / partial | completed | entered-in-error | health-unknown</t>
+    <t>部分的 | 完了 | エラー入力 | 不明 / partial | completed | entered-in-error | health-unknown</t>
   </si>
   <si>
     <t>特定の家族の家族歴史の記録のステータスを指定するコード。 / A code specifying the status of the record of the family history of a specific family member.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
@@ -1280,17 +1280,17 @@
   <dimension ref="A1:AN36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.2109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.2109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.19140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.19140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="253.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1299,26 +1299,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="147.171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.70703125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="49.2109375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="126.17578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="43.47265625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="42.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="28.1484375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="188.0234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="161.19921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
@@ -789,10 +789,10 @@
     <t>FamilyMemberHistory.reasonCode</t>
   </si>
   <si>
-    <t>なぜ家族の歴史が演奏されたのですか？ / Why was family member history performed?</t>
-  </si>
-  <si>
-    <t>家族の歴史がコーディングされた形式またはテキスト形式で発生した理由について説明します。 / Describes why the family member history occurred in coded or textual form.</t>
+    <t>家族歴が作成された理由 / Why was family member history performed?</t>
+  </si>
+  <si>
+    <t>家族歴がコーディングされた形式またはテキスト形式で発生した理由について説明します。 / Describes why the family member history occurred in coded or textual form.</t>
   </si>
   <si>
     <t>テキストの理由は、ReasonCode.textを使用してキャプチャできます。 / Textual reasons can be captured using reasonCode.text.</t>
@@ -817,7 +817,7 @@
 </t>
   </si>
   <si>
-    <t>この家族の歴史イベントを正当化する条件、観察、アレルギーへの耐性、またはアンケートのサンキアが示すことを示します。 / Indicates a Condition, Observation, AllergyIntolerance, or QuestionnaireResponse that justifies this family member history event.</t>
+    <t>家族歴がコーディングされた形式またはテキスト形式で発生した理由について説明します。 / Indicates a Condition, Observation, AllergyIntolerance, or QuestionnaireResponse that justifies this family member history event.</t>
   </si>
   <si>
     <t>Event.reasonReference</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
@@ -368,7 +368,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -501,7 +501,7 @@
     <t>FamilyMemberHistory.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|Questionnaire|ActivityDefinition|Measure|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|Questionnaire|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -581,7 +581,7 @@
     <t>家族の歴史が利用できない理由を説明するコード。 / Codes describing the reason why a family member's history is not available.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/history-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/history-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>.reasonCode</t>
@@ -696,7 +696,7 @@
     <t>出生登録に文書化された出生時に割り当てられた性別を説明するコード。 / Codes describing the sex assigned at birth as documented on the birth registration.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender</t>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
   </si>
   <si>
     <t>FamilyMemberHistory.born[x]</t>
@@ -801,7 +801,7 @@
     <t>家族の歴史が行われた理由を示すコード。 / Codes indicating why the family member history was done.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -915,7 +915,7 @@
     <t>状態または診断の識別。 / Identification of the Condition or diagnosis.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>.value</t>
@@ -933,7 +933,7 @@
     <t>患者の状態の結果。例えば死、永久障害、一時的な障害など。 / The result of the condition for the patient; e.g. death, permanent disability, temporary disability, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-outcome</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-outcome|4.0.1</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=OUTC)].target[classCode=OBS, moodCode=EVN, code=ActCode#ASSERTION].value</t>
@@ -1305,7 +1305,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="126.17578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.47265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="44.51171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-familymemberhistory.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
